--- a/OMOP Analysis/Results/SecondaryCareAnalysis/Comparison/OP/combined_data_costs_all.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/Comparison/OP/combined_data_costs_all.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -367,17 +367,32 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>mean_visit_costs</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>n_exposed</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>se_costs</t>
+          <t>sd_visit_costs</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>se_visit_costs</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ci_lower</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ci_upper</t>
         </is>
       </c>
     </row>
@@ -391,13 +406,22 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>267.4260983171749</v>
+        <v>5494510.779550237</v>
       </c>
       <c r="D2">
-        <v>5485444.128681892</v>
+        <v>239.9349685393117</v>
       </c>
       <c r="E2">
-        <v>6.078672600721845E-05</v>
+        <v>332.9747041174446</v>
+      </c>
+      <c r="F2">
+        <v>0.1420517952807342</v>
+      </c>
+      <c r="G2">
+        <v>239.6565520752908</v>
+      </c>
+      <c r="H2">
+        <v>240.2133850033325</v>
       </c>
     </row>
     <row r="3">
@@ -410,13 +434,22 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>177.5685817925271</v>
+        <v>3650312.155918934</v>
       </c>
       <c r="D3">
-        <v>3642286.749728315</v>
+        <v>159.4022775510452</v>
       </c>
       <c r="E3">
-        <v>6.745706401948583E-05</v>
+        <v>250.7924317268321</v>
+      </c>
+      <c r="F3">
+        <v>0.1312651454503875</v>
+      </c>
+      <c r="G3">
+        <v>159.1450025082301</v>
+      </c>
+      <c r="H3">
+        <v>159.6595525938602</v>
       </c>
     </row>
     <row r="4">
@@ -429,13 +462,22 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>117.5850380652402</v>
+        <v>2408903.593355643</v>
       </c>
       <c r="D4">
-        <v>2411904.300794208</v>
+        <v>105.1922966530849</v>
       </c>
       <c r="E4">
-        <v>9.207607527184541E-05</v>
+        <v>214.5947263633067</v>
+      </c>
+      <c r="F4">
+        <v>0.1382640695190789</v>
+      </c>
+      <c r="G4">
+        <v>104.9213039203099</v>
+      </c>
+      <c r="H4">
+        <v>105.4632893858598</v>
       </c>
     </row>
     <row r="5">
@@ -448,13 +490,22 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>83.8142557477736</v>
+        <v>1714228.064076897</v>
       </c>
       <c r="D5">
-        <v>1719198.013898332</v>
+        <v>74.85712070204791</v>
       </c>
       <c r="E5">
-        <v>0.0001485117756904702</v>
+        <v>242.2549736423748</v>
+      </c>
+      <c r="F5">
+        <v>0.1850284035788897</v>
+      </c>
+      <c r="G5">
+        <v>74.4944714388605</v>
+      </c>
+      <c r="H5">
+        <v>75.21976996523532</v>
       </c>
     </row>
     <row r="6">
@@ -467,13 +518,22 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>64.48916460712074</v>
+        <v>1317345.991485735</v>
       </c>
       <c r="D6">
-        <v>1322801.744421261</v>
+        <v>57.52602582907141</v>
       </c>
       <c r="E6">
-        <v>0.000117517367215279</v>
+        <v>147.0654534151965</v>
+      </c>
+      <c r="F6">
+        <v>0.1281329246569231</v>
+      </c>
+      <c r="G6">
+        <v>57.27488968076844</v>
+      </c>
+      <c r="H6">
+        <v>57.77716197737439</v>
       </c>
     </row>
     <row r="7">
@@ -486,13 +546,22 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>52.50025536727367</v>
+        <v>1071367.04528883</v>
       </c>
       <c r="D7">
-        <v>1076885.238093518</v>
+        <v>46.78458713051661</v>
       </c>
       <c r="E7">
-        <v>0.000129684351364122</v>
+        <v>132.3562950102401</v>
+      </c>
+      <c r="F7">
+        <v>0.1278720005871912</v>
+      </c>
+      <c r="G7">
+        <v>46.53396233159386</v>
+      </c>
+      <c r="H7">
+        <v>47.03521192943936</v>
       </c>
     </row>
     <row r="8">
@@ -505,13 +574,22 @@
         <v>7</v>
       </c>
       <c r="C8">
-        <v>45.26013133024821</v>
+        <v>924180.6154742212</v>
       </c>
       <c r="D8">
-        <v>928375.8138460512</v>
+        <v>40.35723211677821</v>
       </c>
       <c r="E8">
-        <v>0.0001433890430444194</v>
+        <v>126.3751732634587</v>
+      </c>
+      <c r="F8">
+        <v>0.13145688484318</v>
+      </c>
+      <c r="G8">
+        <v>40.09958101952941</v>
+      </c>
+      <c r="H8">
+        <v>40.61488321402702</v>
       </c>
     </row>
     <row r="9">
@@ -524,13 +602,22 @@
         <v>8</v>
       </c>
       <c r="C9">
-        <v>39.12847841972516</v>
+        <v>798476.8602301812</v>
       </c>
       <c r="D9">
-        <v>802603.3493454024</v>
+        <v>34.86798516289002</v>
       </c>
       <c r="E9">
-        <v>0.0001528633479267604</v>
+        <v>116.1248323441114</v>
+      </c>
+      <c r="F9">
+        <v>0.1299552809750304</v>
+      </c>
+      <c r="G9">
+        <v>34.61327710648055</v>
+      </c>
+      <c r="H9">
+        <v>35.12269321929949</v>
       </c>
     </row>
     <row r="10">
@@ -543,13 +630,22 @@
         <v>9</v>
       </c>
       <c r="C10">
-        <v>35.1076427545736</v>
+        <v>715756.4824479452</v>
       </c>
       <c r="D10">
-        <v>720127.9681818136</v>
+        <v>31.25574159161333</v>
       </c>
       <c r="E10">
-        <v>0.0001565718224677443</v>
+        <v>106.3377679974427</v>
+      </c>
+      <c r="F10">
+        <v>0.1256912065930439</v>
+      </c>
+      <c r="G10">
+        <v>31.009390936931</v>
+      </c>
+      <c r="H10">
+        <v>31.50209224629566</v>
       </c>
     </row>
     <row r="11">
@@ -562,13 +658,22 @@
         <v>10</v>
       </c>
       <c r="C11">
-        <v>33.8655521671895</v>
+        <v>690340.4040947576</v>
       </c>
       <c r="D11">
-        <v>694650.206053391</v>
+        <v>30.14586917444356</v>
       </c>
       <c r="E11">
-        <v>0.0001611345949869987</v>
+        <v>105.5725427201309</v>
+      </c>
+      <c r="F11">
+        <v>0.1270630674423223</v>
+      </c>
+      <c r="G11">
+        <v>29.89682970185319</v>
+      </c>
+      <c r="H11">
+        <v>30.39490864703393</v>
       </c>
     </row>
     <row r="12">
@@ -581,13 +686,22 @@
         <v>11</v>
       </c>
       <c r="C12">
-        <v>31.49456900304011</v>
+        <v>642291.4941806889</v>
       </c>
       <c r="D12">
-        <v>646016.5993903588</v>
+        <v>28.04766350134012</v>
       </c>
       <c r="E12">
-        <v>0.0001761698577487557</v>
+        <v>108.478972049995</v>
+      </c>
+      <c r="F12">
+        <v>0.1353566121342523</v>
+      </c>
+      <c r="G12">
+        <v>27.78236891655311</v>
+      </c>
+      <c r="H12">
+        <v>28.31295808612714</v>
       </c>
     </row>
     <row r="13">
@@ -600,13 +714,22 @@
         <v>12</v>
       </c>
       <c r="C13">
-        <v>32.45445208232656</v>
+        <v>661816.1480086134</v>
       </c>
       <c r="D13">
-        <v>665705.7211126825</v>
+        <v>28.90026847199185</v>
       </c>
       <c r="E13">
-        <v>0.0001692105147432927</v>
+        <v>106.5692022019825</v>
+      </c>
+      <c r="F13">
+        <v>0.1309975082323722</v>
+      </c>
+      <c r="G13">
+        <v>28.64351760423152</v>
+      </c>
+      <c r="H13">
+        <v>29.15701933975218</v>
       </c>
     </row>
     <row r="14">
@@ -619,13 +742,22 @@
         <v>13</v>
       </c>
       <c r="C14">
-        <v>27.73856503742267</v>
+        <v>565143.902482948</v>
       </c>
       <c r="D14">
-        <v>568973.4460476139</v>
+        <v>24.67877303418987</v>
       </c>
       <c r="E14">
-        <v>0.000171777982195671</v>
+        <v>92.17596374757713</v>
+      </c>
+      <c r="F14">
+        <v>0.12261346454805</v>
+      </c>
+      <c r="G14">
+        <v>24.43845454496671</v>
+      </c>
+      <c r="H14">
+        <v>24.91909152341303</v>
       </c>
     </row>
     <row r="15">
@@ -638,13 +770,22 @@
         <v>14</v>
       </c>
       <c r="C15">
-        <v>27.96628581828667</v>
+        <v>570019.4803578487</v>
       </c>
       <c r="D15">
-        <v>573644.4547046963</v>
+        <v>24.89168036497156</v>
       </c>
       <c r="E15">
-        <v>0.0001733743893080069</v>
+        <v>93.90313186165113</v>
+      </c>
+      <c r="F15">
+        <v>0.1243756112640864</v>
+      </c>
+      <c r="G15">
+        <v>24.64790812871821</v>
+      </c>
+      <c r="H15">
+        <v>25.13545260122491</v>
       </c>
     </row>
     <row r="16">
@@ -657,13 +798,22 @@
         <v>15</v>
       </c>
       <c r="C16">
-        <v>26.02605865231817</v>
+        <v>530477.4139324977</v>
       </c>
       <c r="D16">
-        <v>533846.5150763502</v>
+        <v>23.16495257347151</v>
       </c>
       <c r="E16">
-        <v>0.0001905700229540567</v>
+        <v>96.08668468648827</v>
+      </c>
+      <c r="F16">
+        <v>0.131925807209034</v>
+      </c>
+      <c r="G16">
+        <v>22.9063821527417</v>
+      </c>
+      <c r="H16">
+        <v>23.42352299420133</v>
       </c>
     </row>
     <row r="17">
@@ -676,13 +826,22 @@
         <v>16</v>
       </c>
       <c r="C17">
-        <v>25.82319427292195</v>
+        <v>526594.4139094448</v>
       </c>
       <c r="D17">
-        <v>529685.360926175</v>
+        <v>22.99538925368755</v>
       </c>
       <c r="E17">
-        <v>0.0001879273448939944</v>
+        <v>93.96220780186685</v>
+      </c>
+      <c r="F17">
+        <v>0.1294836963985151</v>
+      </c>
+      <c r="G17">
+        <v>22.74160528884386</v>
+      </c>
+      <c r="H17">
+        <v>23.24917321853123</v>
       </c>
     </row>
     <row r="18">
@@ -695,13 +854,22 @@
         <v>17</v>
       </c>
       <c r="C18">
-        <v>25.40884620076964</v>
+        <v>518320.9729554538</v>
       </c>
       <c r="D18">
-        <v>521186.2532701868</v>
+        <v>22.6341036225089</v>
       </c>
       <c r="E18">
-        <v>0.0001913877417079292</v>
+        <v>94.30200994239821</v>
+      </c>
+      <c r="F18">
+        <v>0.1309849981374104</v>
+      </c>
+      <c r="G18">
+        <v>22.37737714414485</v>
+      </c>
+      <c r="H18">
+        <v>22.89083010087295</v>
       </c>
     </row>
     <row r="19">
@@ -714,13 +882,22 @@
         <v>18</v>
       </c>
       <c r="C19">
-        <v>23.42688711634395</v>
+        <v>477801.265396152</v>
       </c>
       <c r="D19">
-        <v>480532.3085304471</v>
+        <v>20.86468407843459</v>
       </c>
       <c r="E19">
-        <v>0.0002027210744967073</v>
+        <v>92.00852400879519</v>
+      </c>
+      <c r="F19">
+        <v>0.1331080790800818</v>
+      </c>
+      <c r="G19">
+        <v>20.60379637650503</v>
+      </c>
+      <c r="H19">
+        <v>21.12557178036414</v>
       </c>
     </row>
     <row r="20">
@@ -733,13 +910,22 @@
         <v>19</v>
       </c>
       <c r="C20">
-        <v>22.56575520825327</v>
+        <v>459989.4492114071</v>
       </c>
       <c r="D20">
-        <v>462868.770831691</v>
+        <v>20.08687551141516</v>
       </c>
       <c r="E20">
-        <v>0.0002126500982887961</v>
+        <v>93.02407101893301</v>
+      </c>
+      <c r="F20">
+        <v>0.1371580829772306</v>
+      </c>
+      <c r="G20">
+        <v>19.81804990123213</v>
+      </c>
+      <c r="H20">
+        <v>20.35570112159819</v>
       </c>
     </row>
     <row r="21">
@@ -752,13 +938,22 @@
         <v>20</v>
       </c>
       <c r="C21">
-        <v>22.01925179730982</v>
+        <v>448839.4741488203</v>
       </c>
       <c r="D21">
-        <v>451658.8928664189</v>
+        <v>19.59997703706639</v>
       </c>
       <c r="E21">
-        <v>0.0001996507636552331</v>
+        <v>85.16948665845014</v>
+      </c>
+      <c r="F21">
+        <v>0.1271272074673038</v>
+      </c>
+      <c r="G21">
+        <v>19.35081161706097</v>
+      </c>
+      <c r="H21">
+        <v>19.84914245707182</v>
       </c>
     </row>
     <row r="22">
@@ -771,13 +966,22 @@
         <v>21</v>
       </c>
       <c r="C22">
-        <v>21.24468693439529</v>
+        <v>432751.4296834928</v>
       </c>
       <c r="D22">
-        <v>435771.0183983162</v>
+        <v>18.89744234425732</v>
       </c>
       <c r="E22">
-        <v>0.0002193424109273715</v>
+        <v>89.45644067974689</v>
+      </c>
+      <c r="F22">
+        <v>0.1359854236703122</v>
+      </c>
+      <c r="G22">
+        <v>18.63091506598789</v>
+      </c>
+      <c r="H22">
+        <v>19.16396962252676</v>
       </c>
     </row>
     <row r="23">
@@ -790,13 +994,22 @@
         <v>22</v>
       </c>
       <c r="C23">
-        <v>19.51858614770136</v>
+        <v>397724.8638907074</v>
       </c>
       <c r="D23">
-        <v>400365.2390616502</v>
+        <v>17.36789798649378</v>
       </c>
       <c r="E23">
-        <v>0.000214745170033331</v>
+        <v>81.10807095430597</v>
+      </c>
+      <c r="F23">
+        <v>0.1286093968456907</v>
+      </c>
+      <c r="G23">
+        <v>17.11582743349448</v>
+      </c>
+      <c r="H23">
+        <v>17.61996853949307</v>
       </c>
     </row>
     <row r="24">
@@ -809,13 +1022,22 @@
         <v>23</v>
       </c>
       <c r="C24">
-        <v>19.34598857111079</v>
+        <v>393998.8711241712</v>
       </c>
       <c r="D24">
-        <v>396824.9175706246</v>
+        <v>17.20519087878477</v>
       </c>
       <c r="E24">
-        <v>0.0002359537199074573</v>
+        <v>87.89127969482162</v>
+      </c>
+      <c r="F24">
+        <v>0.1400226520789721</v>
+      </c>
+      <c r="G24">
+        <v>16.9307506806077</v>
+      </c>
+      <c r="H24">
+        <v>17.47963107696184</v>
       </c>
     </row>
     <row r="25">
@@ -828,13 +1050,22 @@
         <v>24</v>
       </c>
       <c r="C25">
-        <v>17.58526776693666</v>
+        <v>358037.2994391443</v>
       </c>
       <c r="D25">
-        <v>360709.0124354047</v>
+        <v>15.63481656939495</v>
       </c>
       <c r="E25">
-        <v>0.0002222982628316175</v>
+        <v>75.50444696482177</v>
+      </c>
+      <c r="F25">
+        <v>0.1261851924882404</v>
+      </c>
+      <c r="G25">
+        <v>15.38749730065712</v>
+      </c>
+      <c r="H25">
+        <v>15.88213583813278</v>
       </c>
     </row>
     <row r="26">
@@ -847,13 +1078,22 @@
         <v>1</v>
       </c>
       <c r="C26">
+        <v>6009021.335224808</v>
+      </c>
+      <c r="D26">
         <v>260.0632448379126</v>
       </c>
-      <c r="D26">
-        <v>6009021.335224808</v>
-      </c>
       <c r="E26">
-        <v>6.330164048504995E-05</v>
+        <v>380.3809082293956</v>
+      </c>
+      <c r="F26">
+        <v>0.1551732435058118</v>
+      </c>
+      <c r="G26">
+        <v>259.7591108080168</v>
+      </c>
+      <c r="H26">
+        <v>260.3673788678083</v>
       </c>
     </row>
     <row r="27">
@@ -866,13 +1106,22 @@
         <v>2</v>
       </c>
       <c r="C27">
+        <v>3874800.386053412</v>
+      </c>
+      <c r="D27">
         <v>167.6967188632135</v>
       </c>
-      <c r="D27">
-        <v>3874800.386053412</v>
-      </c>
       <c r="E27">
-        <v>7.163432598909813E-05</v>
+        <v>277.5687139972334</v>
+      </c>
+      <c r="F27">
+        <v>0.1410086796720421</v>
+      </c>
+      <c r="G27">
+        <v>167.4203468432189</v>
+      </c>
+      <c r="H27">
+        <v>167.9730908832082</v>
       </c>
     </row>
     <row r="28">
@@ -885,13 +1134,22 @@
         <v>3</v>
       </c>
       <c r="C28">
+        <v>2562622.612112426</v>
+      </c>
+      <c r="D28">
         <v>110.9072367399128</v>
       </c>
-      <c r="D28">
-        <v>2562622.612112426</v>
-      </c>
       <c r="E28">
-        <v>9.408272249784044E-05</v>
+        <v>241.0985120820644</v>
+      </c>
+      <c r="F28">
+        <v>0.1506094432858016</v>
+      </c>
+      <c r="G28">
+        <v>110.6120475159187</v>
+      </c>
+      <c r="H28">
+        <v>111.2024259639069</v>
       </c>
     </row>
     <row r="29">
@@ -904,13 +1162,22 @@
         <v>4</v>
       </c>
       <c r="C29">
+        <v>1811263.543490788</v>
+      </c>
+      <c r="D29">
         <v>78.38931634600483</v>
       </c>
-      <c r="D29">
-        <v>1811263.543490788</v>
-      </c>
       <c r="E29">
-        <v>0.000130619252771341</v>
+        <v>236.585890622738</v>
+      </c>
+      <c r="F29">
+        <v>0.1757915590959482</v>
+      </c>
+      <c r="G29">
+        <v>78.04477099115039</v>
+      </c>
+      <c r="H29">
+        <v>78.73386170085928</v>
       </c>
     </row>
     <row r="30">
@@ -923,13 +1190,22 @@
         <v>5</v>
       </c>
       <c r="C30">
+        <v>1408120.427261455</v>
+      </c>
+      <c r="D30">
         <v>60.9417652238144</v>
       </c>
-      <c r="D30">
-        <v>1408120.427261455</v>
-      </c>
       <c r="E30">
-        <v>0.0001107379862370319</v>
+        <v>155.9324204941625</v>
+      </c>
+      <c r="F30">
+        <v>0.131406401041158</v>
+      </c>
+      <c r="G30">
+        <v>60.68421318905399</v>
+      </c>
+      <c r="H30">
+        <v>61.19931725857481</v>
       </c>
     </row>
     <row r="31">
@@ -942,13 +1218,22 @@
         <v>6</v>
       </c>
       <c r="C31">
+        <v>1140221.413694534</v>
+      </c>
+      <c r="D31">
         <v>49.34741684820109</v>
       </c>
-      <c r="D31">
-        <v>1140221.413694534</v>
-      </c>
       <c r="E31">
-        <v>0.0001243741298059177</v>
+        <v>141.814046114331</v>
+      </c>
+      <c r="F31">
+        <v>0.1328081269340329</v>
+      </c>
+      <c r="G31">
+        <v>49.08711742624359</v>
+      </c>
+      <c r="H31">
+        <v>49.60771627015858</v>
       </c>
     </row>
     <row r="32">
@@ -961,13 +1246,22 @@
         <v>7</v>
       </c>
       <c r="C32">
+        <v>992482.877903262</v>
+      </c>
+      <c r="D32">
         <v>42.95347000360348</v>
       </c>
-      <c r="D32">
-        <v>992482.877903262</v>
-      </c>
       <c r="E32">
-        <v>0.0001434626115214932</v>
+        <v>142.3841855543693</v>
+      </c>
+      <c r="F32">
+        <v>0.1429223813788123</v>
+      </c>
+      <c r="G32">
+        <v>42.67334694189692</v>
+      </c>
+      <c r="H32">
+        <v>43.23359306531005</v>
       </c>
     </row>
     <row r="33">
@@ -980,13 +1274,22 @@
         <v>8</v>
       </c>
       <c r="C33">
+        <v>864152.9207462566</v>
+      </c>
+      <c r="D33">
         <v>37.39950319164964</v>
       </c>
-      <c r="D33">
-        <v>864152.9207462566</v>
-      </c>
       <c r="E33">
-        <v>0.0001528051895468456</v>
+        <v>132.047050852092</v>
+      </c>
+      <c r="F33">
+        <v>0.1420474379725164</v>
+      </c>
+      <c r="G33">
+        <v>37.12109493917794</v>
+      </c>
+      <c r="H33">
+        <v>37.67791144412135</v>
       </c>
     </row>
     <row r="34">
@@ -999,13 +1302,22 @@
         <v>9</v>
       </c>
       <c r="C34">
+        <v>773262.6539671132</v>
+      </c>
+      <c r="D34">
         <v>33.4658813281015</v>
       </c>
-      <c r="D34">
-        <v>773262.6539671132</v>
-      </c>
       <c r="E34">
-        <v>0.0001533932041893416</v>
+        <v>118.6132361719696</v>
+      </c>
+      <c r="F34">
+        <v>0.1348868576092034</v>
+      </c>
+      <c r="G34">
+        <v>33.20150753138283</v>
+      </c>
+      <c r="H34">
+        <v>33.73025512482018</v>
       </c>
     </row>
     <row r="35">
@@ -1018,13 +1330,22 @@
         <v>10</v>
       </c>
       <c r="C35">
+        <v>743612.6480470877</v>
+      </c>
+      <c r="D35">
         <v>32.18266459132207</v>
       </c>
-      <c r="D35">
-        <v>743612.6480470877</v>
-      </c>
       <c r="E35">
-        <v>0.0001548291503112294</v>
+        <v>115.1329144578138</v>
+      </c>
+      <c r="F35">
+        <v>0.1335137869972939</v>
+      </c>
+      <c r="G35">
+        <v>31.92098195143121</v>
+      </c>
+      <c r="H35">
+        <v>32.44434723121292</v>
       </c>
     </row>
     <row r="36">
@@ -1037,13 +1358,22 @@
         <v>11</v>
       </c>
       <c r="C36">
+        <v>695702.4583912443</v>
+      </c>
+      <c r="D36">
         <v>30.10916897737576</v>
       </c>
-      <c r="D36">
-        <v>695702.4583912443</v>
-      </c>
       <c r="E36">
-        <v>0.0001749291191552701</v>
+        <v>121.6986182405363</v>
+      </c>
+      <c r="F36">
+        <v>0.1459062441817708</v>
+      </c>
+      <c r="G36">
+        <v>29.82319749613367</v>
+      </c>
+      <c r="H36">
+        <v>30.39514045861785</v>
       </c>
     </row>
     <row r="37">
@@ -1056,13 +1386,22 @@
         <v>12</v>
       </c>
       <c r="C37">
+        <v>717856.5191662922</v>
+      </c>
+      <c r="D37">
         <v>31.06797018810231</v>
       </c>
-      <c r="D37">
-        <v>717856.5191662922</v>
-      </c>
       <c r="E37">
-        <v>0.000162574179253112</v>
+        <v>116.7049344249558</v>
+      </c>
+      <c r="F37">
+        <v>0.1377432718100069</v>
+      </c>
+      <c r="G37">
+        <v>30.79799788104602</v>
+      </c>
+      <c r="H37">
+        <v>31.33794249515861</v>
       </c>
     </row>
     <row r="38">
@@ -1075,13 +1414,22 @@
         <v>13</v>
       </c>
       <c r="C38">
+        <v>606753.0856206736</v>
+      </c>
+      <c r="D38">
         <v>26.25954668141061</v>
       </c>
-      <c r="D38">
-        <v>606753.0856206736</v>
-      </c>
       <c r="E38">
-        <v>0.0001705449040442034</v>
+        <v>103.4786467657021</v>
+      </c>
+      <c r="F38">
+        <v>0.1328448564426967</v>
+      </c>
+      <c r="G38">
+        <v>25.99917502785546</v>
+      </c>
+      <c r="H38">
+        <v>26.51991833496576</v>
       </c>
     </row>
     <row r="39">
@@ -1094,13 +1442,22 @@
         <v>14</v>
       </c>
       <c r="C39">
+        <v>621221.2767165386</v>
+      </c>
+      <c r="D39">
         <v>26.88571265976537</v>
       </c>
-      <c r="D39">
-        <v>621221.2767165386</v>
-      </c>
       <c r="E39">
-        <v>0.000175356452239333</v>
+        <v>108.9351591406012</v>
+      </c>
+      <c r="F39">
+        <v>0.1382117326098728</v>
+      </c>
+      <c r="G39">
+        <v>26.61482211381512</v>
+      </c>
+      <c r="H39">
+        <v>27.15660320571562</v>
       </c>
     </row>
     <row r="40">
@@ -1113,13 +1470,22 @@
         <v>15</v>
       </c>
       <c r="C40">
+        <v>578977.5324440817</v>
+      </c>
+      <c r="D40">
         <v>25.05745401385276</v>
       </c>
-      <c r="D40">
-        <v>578977.5324440817</v>
-      </c>
       <c r="E40">
-        <v>0.0001876684601641608</v>
+        <v>108.6558219834263</v>
+      </c>
+      <c r="F40">
+        <v>0.1427980069871452</v>
+      </c>
+      <c r="G40">
+        <v>24.77757447799881</v>
+      </c>
+      <c r="H40">
+        <v>25.3373335497067</v>
       </c>
     </row>
     <row r="41">
@@ -1132,13 +1498,22 @@
         <v>16</v>
       </c>
       <c r="C41">
+        <v>569198.2585856941</v>
+      </c>
+      <c r="D41">
         <v>24.63421875641366</v>
       </c>
-      <c r="D41">
-        <v>569198.2585856941</v>
-      </c>
       <c r="E41">
-        <v>0.0001830452416805223</v>
+        <v>104.1890328069508</v>
+      </c>
+      <c r="F41">
+        <v>0.1380989018443238</v>
+      </c>
+      <c r="G41">
+        <v>24.36354930693151</v>
+      </c>
+      <c r="H41">
+        <v>24.90488820589582</v>
       </c>
     </row>
     <row r="42">
@@ -1151,13 +1526,22 @@
         <v>17</v>
       </c>
       <c r="C42">
+        <v>569573.8716341355</v>
+      </c>
+      <c r="D42">
         <v>24.65047483918183</v>
       </c>
-      <c r="D42">
-        <v>569573.8716341355</v>
-      </c>
       <c r="E42">
-        <v>0.0001851950437818433</v>
+        <v>105.4822580942777</v>
+      </c>
+      <c r="F42">
+        <v>0.1397669181386549</v>
+      </c>
+      <c r="G42">
+        <v>24.37653613126943</v>
+      </c>
+      <c r="H42">
+        <v>24.92441354709424</v>
       </c>
     </row>
     <row r="43">
@@ -1170,13 +1554,22 @@
         <v>18</v>
       </c>
       <c r="C43">
+        <v>516302.7408298189</v>
+      </c>
+      <c r="D43">
         <v>22.34496411450787</v>
       </c>
-      <c r="D43">
-        <v>516302.7408298189</v>
-      </c>
       <c r="E43">
-        <v>0.0001940941223272555</v>
+        <v>100.2113273365202</v>
+      </c>
+      <c r="F43">
+        <v>0.1394647970874055</v>
+      </c>
+      <c r="G43">
+        <v>22.07161749429969</v>
+      </c>
+      <c r="H43">
+        <v>22.61831073471605</v>
       </c>
     </row>
     <row r="44">
@@ -1189,13 +1582,22 @@
         <v>19</v>
       </c>
       <c r="C44">
+        <v>514733.9971963592</v>
+      </c>
+      <c r="D44">
         <v>22.27707076933953</v>
       </c>
-      <c r="D44">
-        <v>514733.9971963592</v>
-      </c>
       <c r="E44">
-        <v>0.0003258334327353771</v>
+        <v>167.7175452520917</v>
+      </c>
+      <c r="F44">
+        <v>0.233769081572906</v>
+      </c>
+      <c r="G44">
+        <v>21.81889071137391</v>
+      </c>
+      <c r="H44">
+        <v>22.73525082730514</v>
       </c>
     </row>
     <row r="45">
@@ -1208,13 +1610,22 @@
         <v>20</v>
       </c>
       <c r="C45">
+        <v>487329.5357204647</v>
+      </c>
+      <c r="D45">
         <v>21.09103850603586</v>
       </c>
-      <c r="D45">
-        <v>487329.5357204647</v>
-      </c>
       <c r="E45">
-        <v>0.0001976180307409706</v>
+        <v>96.3051031709897</v>
+      </c>
+      <c r="F45">
+        <v>0.1379551551735454</v>
+      </c>
+      <c r="G45">
+        <v>20.82065069885923</v>
+      </c>
+      <c r="H45">
+        <v>21.3614263132125</v>
       </c>
     </row>
     <row r="46">
@@ -1227,13 +1638,22 @@
         <v>21</v>
       </c>
       <c r="C46">
+        <v>470884.9898333896</v>
+      </c>
+      <c r="D46">
         <v>20.37933825990607</v>
       </c>
-      <c r="D46">
-        <v>470884.9898333896</v>
-      </c>
       <c r="E46">
-        <v>0.0002100668630780616</v>
+        <v>98.91733268484508</v>
+      </c>
+      <c r="F46">
+        <v>0.1441501085020556</v>
+      </c>
+      <c r="G46">
+        <v>20.09680851265737</v>
+      </c>
+      <c r="H46">
+        <v>20.66186800715477</v>
       </c>
     </row>
     <row r="47">
@@ -1246,13 +1666,22 @@
         <v>22</v>
       </c>
       <c r="C47">
+        <v>427395.6459560183</v>
+      </c>
+      <c r="D47">
         <v>18.49717155526782</v>
       </c>
-      <c r="D47">
-        <v>427395.6459560183</v>
-      </c>
       <c r="E47">
-        <v>0.0002037103710353109</v>
+        <v>87.06492561657687</v>
+      </c>
+      <c r="F47">
+        <v>0.1331766807722531</v>
+      </c>
+      <c r="G47">
+        <v>18.23614931816902</v>
+      </c>
+      <c r="H47">
+        <v>18.75819379236663</v>
       </c>
     </row>
     <row r="48">
@@ -1265,13 +1694,22 @@
         <v>23</v>
       </c>
       <c r="C48">
+        <v>420884.8489444911</v>
+      </c>
+      <c r="D48">
         <v>18.21539206026534</v>
       </c>
-      <c r="D48">
-        <v>420884.8489444911</v>
-      </c>
       <c r="E48">
-        <v>0.0002203464443795619</v>
+        <v>92.74047995814763</v>
+      </c>
+      <c r="F48">
+        <v>0.1429511630202142</v>
+      </c>
+      <c r="G48">
+        <v>17.93521212346489</v>
+      </c>
+      <c r="H48">
+        <v>18.4955719970658</v>
       </c>
     </row>
     <row r="49">
@@ -1284,13 +1722,22 @@
         <v>24</v>
       </c>
       <c r="C49">
+        <v>381732.1198249586</v>
+      </c>
+      <c r="D49">
         <v>16.52090884726731</v>
       </c>
-      <c r="D49">
-        <v>381732.1198249586</v>
-      </c>
       <c r="E49">
-        <v>0.0002115932055600384</v>
+        <v>80.77192289899168</v>
+      </c>
+      <c r="F49">
+        <v>0.1307317485748811</v>
+      </c>
+      <c r="G49">
+        <v>16.26467851598853</v>
+      </c>
+      <c r="H49">
+        <v>16.7771391785461</v>
       </c>
     </row>
   </sheetData>
